--- a/data/trans_orig/cron_mort_index-Clase-trans_orig.xlsx
+++ b/data/trans_orig/cron_mort_index-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de cronicidad física en base a la mortalidad</t>
+          <t>Índice de cronicidad física en base a la mortalidad (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,7 +716,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,08</t>
+          <t>0,03; 0,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,05</t>
+          <t>0,03; 0,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,26</t>
+          <t>0,18; 0,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,01; 0,04</t>
+          <t>0,01; 0,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,07</t>
+          <t>0,03; 0,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,13</t>
+          <t>0,05; 0,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,33</t>
+          <t>0,21; 0,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,3</t>
+          <t>0,09; 0,29</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,08</t>
+          <t>0,05; 0,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,1</t>
+          <t>0,08; 0,11</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,23</t>
+          <t>0,13; 0,23</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,1</t>
+          <t>0,06; 0,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,16</t>
+          <t>0,1; 0,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,15</t>
+          <t>0,11; 0,14</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,45</t>
+          <t>0,27; 0,44</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,03</t>
+          <t>0,0; 0,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,22</t>
+          <t>0,02; 0,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
+          <t>0,14; 0,18</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
           <t>0,13; 0,18</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>0,13; 0,18</t>
-        </is>
-      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
           <t>0,25; 0,31</t>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,26</t>
+          <t>0,2; 0,27</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,12</t>
+          <t>0,09; 0,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,25</t>
+          <t>0,19; 0,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/cron_mort_index-Clase-trans_orig.xlsx
+++ b/data/trans_orig/cron_mort_index-Clase-trans_orig.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,07</t>
+          <t>0,03; 0,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,27</t>
+          <t>0,2; 0,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -746,22 +746,22 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,11</t>
+          <t>0,04; 0,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,17</t>
+          <t>0,12; 0,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,06</t>
+          <t>0,03; 0,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,06</t>
+          <t>0,03; 0,07</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,21</t>
+          <t>0,17; 0,22</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,21</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,09</t>
+          <t>0,04; 0,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,27</t>
+          <t>0,17; 0,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,21</t>
+          <t>0,15; 0,2</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>0,28</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,28</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,07</t>
+          <t>0,04; 0,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,31</t>
+          <t>0,23; 0,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,13</t>
+          <t>0,04; 0,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,34</t>
+          <t>0,2; 0,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,29</t>
+          <t>0,24; 0,32</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>0,17</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,22</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,12</t>
+          <t>0,09; 0,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,3</t>
+          <t>0,24; 0,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1166,19 +1166,19 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>0,04; 0,08</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0,15; 0,19</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>0,05; 0,08</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 0,18</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0,05; 0,08</t>
-        </is>
-      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t>0,08; 0,11</t>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,23</t>
+          <t>0,2; 0,24</t>
         </is>
       </c>
     </row>
@@ -1223,47 +1223,47 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>0,26</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,06</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,12</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0,13</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0,29</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0,06</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0,1</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0,13</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
           <t>0,28</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,13</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0,34</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0,1</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>0,13</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,32</t>
         </is>
       </c>
     </row>
@@ -1276,32 +1276,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0,04; 0,1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0,05; 0,11</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0,1; 0,16</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0,22; 0,31</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>0,04; 0,09</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,06; 0,11</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0,1; 0,16</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,24; 0,34</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,04; 0,09</t>
-        </is>
-      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,14</t>
+          <t>0,1; 0,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,53</t>
+          <t>0,26; 0,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1331,14 +1331,14 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,44</t>
+          <t>0,25; 0,31</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1426,12 +1426,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,04</t>
+          <t>0,0; 0,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,2</t>
+          <t>0,02; 0,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,31</t>
+          <t>0,24; 0,31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,27</t>
+          <t>0,2; 0,26</t>
         </is>
       </c>
     </row>
@@ -1503,47 +1503,47 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
+          <t>0,24</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,07</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,11</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0,06</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0,1</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>0,1</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>0,23</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,1</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0,22</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0,1</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>0,1</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,22</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,06</t>
+          <t>0,05; 0,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,25</t>
+          <t>0,22; 0,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>0,09; 0,12</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0,2; 0,23</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0,06; 0,07</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>0,09; 0,1</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
           <t>0,09; 0,11</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0,19; 0,27</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0,06; 0,07</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0,09; 0,1</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>0,09; 0,11</t>
-        </is>
-      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,25</t>
+          <t>0,22; 0,24</t>
         </is>
       </c>
     </row>
